--- a/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.004844999999999999</v>
+        <v>0.0148</v>
       </c>
       <c r="E2">
-        <v>0.0177</v>
+        <v>0.01885</v>
       </c>
       <c r="F2">
-        <v>0.09735000000000001</v>
+        <v>0.04735</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20659.4</v>
+        <v>20109.99</v>
       </c>
       <c r="L2">
-        <v>0.3497828608192877</v>
+        <v>0.3683971510117646</v>
       </c>
       <c r="M2">
-        <v>11709.6</v>
+        <v>22601.7</v>
       </c>
       <c r="N2">
-        <v>0.0381980350337857</v>
+        <v>0.07893763522728663</v>
       </c>
       <c r="O2">
-        <v>0.5667928400631189</v>
+        <v>1.123904089460015</v>
       </c>
       <c r="P2">
-        <v>9154.6</v>
+        <v>12315.3</v>
       </c>
       <c r="Q2">
-        <v>0.02986333704996709</v>
+        <v>0.04301183800840657</v>
       </c>
       <c r="R2">
-        <v>0.4431203229522638</v>
+        <v>0.6123971220274101</v>
       </c>
       <c r="S2">
-        <v>2555</v>
+        <v>10286.4</v>
       </c>
       <c r="T2">
-        <v>0.2181970349115256</v>
+        <v>0.455116208072844</v>
       </c>
       <c r="U2">
-        <v>233233.2</v>
+        <v>274848.6</v>
       </c>
       <c r="V2">
-        <v>0.7608329870057002</v>
+        <v>0.9599233035360352</v>
       </c>
       <c r="W2">
-        <v>0.1032533671413967</v>
+        <v>0.09763086538398101</v>
       </c>
       <c r="X2">
-        <v>0.07855422606614479</v>
+        <v>0.1192046037750007</v>
       </c>
       <c r="Y2">
-        <v>0.02469914107525187</v>
+        <v>-0.02157373839101968</v>
       </c>
       <c r="Z2">
-        <v>0.07626352561165056</v>
+        <v>0.08591355888322037</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03499150862665689</v>
+        <v>0.05588484603734435</v>
       </c>
       <c r="AC2">
-        <v>-0.03499150862665689</v>
+        <v>-0.05588484603734435</v>
       </c>
       <c r="AD2">
-        <v>675797.5</v>
+        <v>737153.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>675797.5</v>
+        <v>737153.1</v>
       </c>
       <c r="AG2">
-        <v>442564.3</v>
+        <v>462304.5</v>
       </c>
       <c r="AH2">
-        <v>0.6879415253648073</v>
+        <v>0.7202442146698811</v>
       </c>
       <c r="AI2">
-        <v>0.7691513183914686</v>
+        <v>0.8060365833989855</v>
       </c>
       <c r="AJ2">
-        <v>0.590783566882535</v>
+        <v>0.6175356786013881</v>
       </c>
       <c r="AK2">
-        <v>0.6857270044064535</v>
+        <v>0.7226986929176373</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00431</v>
+        <v>0.0141</v>
       </c>
       <c r="E3">
-        <v>0.784</v>
+        <v>0.0545</v>
       </c>
       <c r="F3">
-        <v>0.103</v>
+        <v>0.0707</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4609.6</v>
+        <v>4439.5</v>
       </c>
       <c r="L3">
-        <v>0.3758796428425817</v>
+        <v>0.3735757922550026</v>
       </c>
       <c r="M3">
-        <v>3862.1</v>
+        <v>5426.5</v>
       </c>
       <c r="N3">
-        <v>0.05657469732148743</v>
+        <v>0.08444915465252359</v>
       </c>
       <c r="O3">
-        <v>0.8378384241582782</v>
+        <v>1.222322333596126</v>
       </c>
       <c r="P3">
-        <v>1942.6</v>
+        <v>2580.9</v>
       </c>
       <c r="Q3">
-        <v>0.02845654100533945</v>
+        <v>0.04016489878240084</v>
       </c>
       <c r="R3">
-        <v>0.4214248524817771</v>
+        <v>0.581349251041784</v>
       </c>
       <c r="S3">
-        <v>1919.5</v>
+        <v>2845.6</v>
       </c>
       <c r="T3">
-        <v>0.497009399031615</v>
+        <v>0.5243895697042292</v>
       </c>
       <c r="U3">
-        <v>19530.6</v>
+        <v>26728.5</v>
       </c>
       <c r="V3">
-        <v>0.2860976628018545</v>
+        <v>0.415958579218645</v>
       </c>
       <c r="W3">
-        <v>0.1049140927102276</v>
+        <v>0.09763086538398101</v>
       </c>
       <c r="X3">
-        <v>0.09112761125188278</v>
+        <v>0.1287475869805902</v>
       </c>
       <c r="Y3">
-        <v>0.01378648145834485</v>
+        <v>-0.03111672159660923</v>
       </c>
       <c r="Z3">
-        <v>0.05568440945511147</v>
+        <v>0.049383772893986</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0346950467526972</v>
+        <v>0.05552526584110484</v>
       </c>
       <c r="AC3">
-        <v>-0.0346950467526972</v>
+        <v>-0.05552526584110484</v>
       </c>
       <c r="AD3">
-        <v>216122.7</v>
+        <v>223145.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>216122.7</v>
+        <v>223145.9</v>
       </c>
       <c r="AG3">
-        <v>196592.1</v>
+        <v>196417.4</v>
       </c>
       <c r="AH3">
-        <v>0.7599566367380926</v>
+        <v>0.7764202593218246</v>
       </c>
       <c r="AI3">
-        <v>0.8261729008581968</v>
+        <v>0.8543853959631224</v>
       </c>
       <c r="AJ3">
-        <v>0.7422558386091244</v>
+        <v>0.7534953486141747</v>
       </c>
       <c r="AK3">
-        <v>0.8121479242713922</v>
+        <v>0.8377844866636014</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0189</v>
+        <v>-0.0151</v>
       </c>
       <c r="E4">
-        <v>-0.0602</v>
+        <v>-0.0655</v>
       </c>
       <c r="F4">
-        <v>0.16</v>
+        <v>0.117</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3953.4</v>
+        <v>3668.3</v>
       </c>
       <c r="L4">
-        <v>0.2502326111311547</v>
+        <v>0.295466078145514</v>
       </c>
       <c r="M4">
-        <v>2112.8</v>
+        <v>5103.7</v>
       </c>
       <c r="N4">
-        <v>0.03714284207435952</v>
+        <v>0.09177616376822278</v>
       </c>
       <c r="O4">
-        <v>0.5344260636414226</v>
+        <v>1.391298421612191</v>
       </c>
       <c r="P4">
-        <v>2061.4</v>
+        <v>2794.1</v>
       </c>
       <c r="Q4">
-        <v>0.03623923450022942</v>
+        <v>0.0502442892773461</v>
       </c>
       <c r="R4">
-        <v>0.5214245965498052</v>
+        <v>0.7616879753564321</v>
       </c>
       <c r="S4">
-        <v>51.40000000000009</v>
+        <v>2309.6</v>
       </c>
       <c r="T4">
-        <v>0.02432790609617573</v>
+        <v>0.4525344358014773</v>
       </c>
       <c r="U4">
-        <v>51360.3</v>
+        <v>67616.3</v>
       </c>
       <c r="V4">
-        <v>0.9029096515485268</v>
+        <v>1.215895256813936</v>
       </c>
       <c r="W4">
-        <v>0.08107542758705549</v>
+        <v>0.07030546260200933</v>
       </c>
       <c r="X4">
-        <v>0.08336844689944793</v>
+        <v>0.1196461265906391</v>
       </c>
       <c r="Y4">
-        <v>-0.002293019312392439</v>
+        <v>-0.04934066398862974</v>
       </c>
       <c r="Z4">
-        <v>0.08641405387252163</v>
+        <v>0.08347727744917356</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03485707072656077</v>
+        <v>0.0558661346790262</v>
       </c>
       <c r="AC4">
-        <v>-0.03485707072656077</v>
+        <v>-0.0558661346790262</v>
       </c>
       <c r="AD4">
-        <v>153414.5</v>
+        <v>165537.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>153414.5</v>
+        <v>165537.3</v>
       </c>
       <c r="AG4">
-        <v>102054.2</v>
+        <v>97920.99999999999</v>
       </c>
       <c r="AH4">
-        <v>0.7295114162025624</v>
+        <v>0.7485376282627531</v>
       </c>
       <c r="AI4">
-        <v>0.7460619046414865</v>
+        <v>0.7846764235349883</v>
       </c>
       <c r="AJ4">
-        <v>0.6421035213257053</v>
+        <v>0.6377917727525266</v>
       </c>
       <c r="AK4">
-        <v>0.6615207804910933</v>
+        <v>0.6831084465441009</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Australia and New Zealand Banking Group Limited (ASX:ANZ)</t>
+          <t>ANZ Group Holdings Limited (ASX:ANZ)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.006860000000000001</v>
+        <v>0.0155</v>
       </c>
       <c r="E5">
-        <v>0.0154</v>
+        <v>0.0213</v>
       </c>
       <c r="F5">
-        <v>0.0917</v>
+        <v>0.013</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4463.3</v>
+        <v>4586.4</v>
       </c>
       <c r="L5">
-        <v>0.3425823585398054</v>
+        <v>0.3621432970642578</v>
       </c>
       <c r="M5">
-        <v>2583.6</v>
+        <v>3058.2</v>
       </c>
       <c r="N5">
-        <v>0.04596449653611725</v>
+        <v>0.06393721266200166</v>
       </c>
       <c r="O5">
-        <v>0.578854211009791</v>
+        <v>0.6667974882260598</v>
       </c>
       <c r="P5">
-        <v>2052.7</v>
+        <v>2437.8</v>
       </c>
       <c r="Q5">
-        <v>0.03651932266592656</v>
+        <v>0.05096662645589813</v>
       </c>
       <c r="R5">
-        <v>0.4599063473214886</v>
+        <v>0.5315279958137101</v>
       </c>
       <c r="S5">
-        <v>530.9000000000001</v>
+        <v>620.4000000000001</v>
       </c>
       <c r="T5">
-        <v>0.2054884657067658</v>
+        <v>0.2028644300568962</v>
       </c>
       <c r="U5">
-        <v>96834</v>
+        <v>98013.10000000001</v>
       </c>
       <c r="V5">
-        <v>1.722761285639564</v>
+        <v>2.049141461762486</v>
       </c>
       <c r="W5">
-        <v>0.1015926415725657</v>
+        <v>0.09945786529036735</v>
       </c>
       <c r="X5">
-        <v>0.07374000523284165</v>
+        <v>0.1192046037750007</v>
       </c>
       <c r="Y5">
-        <v>0.02785263633972404</v>
+        <v>-0.01974673848463335</v>
       </c>
       <c r="Z5">
-        <v>0.07248308705714794</v>
+        <v>0.1920852026779024</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03512594652675301</v>
+        <v>0.05588484603734435</v>
       </c>
       <c r="AC5">
-        <v>-0.03512594652675301</v>
+        <v>-0.05588484603734435</v>
       </c>
       <c r="AD5">
-        <v>118889.6</v>
+        <v>141230.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>118889.6</v>
+        <v>141230.5</v>
       </c>
       <c r="AG5">
-        <v>22055.60000000001</v>
+        <v>43217.39999999999</v>
       </c>
       <c r="AH5">
-        <v>0.6789881335159356</v>
+        <v>0.747007063298879</v>
       </c>
       <c r="AI5">
-        <v>0.7204923775055815</v>
+        <v>0.7675191063920208</v>
       </c>
       <c r="AJ5">
-        <v>0.2818095629930416</v>
+        <v>0.474662460858859</v>
       </c>
       <c r="AK5">
-        <v>0.3235021473328484</v>
+        <v>0.5025512814549513</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.014</v>
+        <v>0.0169</v>
       </c>
       <c r="E6">
-        <v>0.02</v>
+        <v>0.0164</v>
       </c>
       <c r="F6">
-        <v>0.04190000000000001</v>
+        <v>0.024</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,90 +1109,203 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>7633.1</v>
+        <v>7421.1</v>
       </c>
       <c r="L6">
-        <v>0.4247052474030057</v>
+        <v>0.423520750582112</v>
       </c>
       <c r="M6">
-        <v>3151.1</v>
+        <v>9013.299999999999</v>
       </c>
       <c r="N6">
-        <v>0.0251700180362098</v>
+        <v>0.07662500733239422</v>
       </c>
       <c r="O6">
-        <v>0.4128204792286227</v>
+        <v>1.214550403578984</v>
       </c>
       <c r="P6">
-        <v>3097.9</v>
+        <v>4502.5</v>
       </c>
       <c r="Q6">
-        <v>0.02474507279184233</v>
+        <v>0.03827722316067422</v>
       </c>
       <c r="R6">
-        <v>0.4058508338682842</v>
+        <v>0.6067159855008017</v>
       </c>
       <c r="S6">
-        <v>53.19999999999982</v>
+        <v>4510.799999999999</v>
       </c>
       <c r="T6">
-        <v>0.01688299324045566</v>
+        <v>0.5004604306968591</v>
       </c>
       <c r="U6">
-        <v>65508.3</v>
+        <v>82234.39999999999</v>
       </c>
       <c r="V6">
-        <v>0.5232601607443251</v>
+        <v>0.6991014947882617</v>
       </c>
       <c r="W6">
-        <v>0.1536954481936541</v>
+        <v>0.1257992663362242</v>
       </c>
       <c r="X6">
-        <v>0.06350549141455263</v>
+        <v>0.09693677260778816</v>
       </c>
       <c r="Y6">
-        <v>0.09018995677910151</v>
+        <v>0.028862493728436</v>
       </c>
       <c r="Z6">
-        <v>0.09377298971417362</v>
+        <v>0.09907071730492188</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03554915530219166</v>
+        <v>0.05725483416356029</v>
       </c>
       <c r="AC6">
-        <v>-0.03554915530219166</v>
+        <v>-0.05725483416356029</v>
       </c>
       <c r="AD6">
-        <v>187370.7</v>
+        <v>204592.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>187370.7</v>
+        <v>204592.1</v>
       </c>
       <c r="AG6">
-        <v>121862.4</v>
+        <v>122357.7</v>
       </c>
       <c r="AH6">
-        <v>0.5994648124075986</v>
+        <v>0.6349438025105767</v>
       </c>
       <c r="AI6">
-        <v>0.7604685283606987</v>
+        <v>0.8030251588940432</v>
       </c>
       <c r="AJ6">
-        <v>0.4932602052174617</v>
+        <v>0.5098526416496935</v>
       </c>
       <c r="AK6">
-        <v>0.6737188481658025</v>
+        <v>0.709146105042068</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Judo Capital Holdings Limited (ASX:JDO)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-5.31</v>
+      </c>
+      <c r="L7">
+        <v>-0.05221238938053097</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>256.3</v>
+      </c>
+      <c r="V7">
+        <v>0.2574327038971475</v>
+      </c>
+      <c r="W7">
+        <v>-0.006584004959702417</v>
+      </c>
+      <c r="X7">
+        <v>0.113814997440816</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1203990024005184</v>
+      </c>
+      <c r="Z7">
+        <v>0.03166054417533155</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05908349431828389</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05908349431828389</v>
+      </c>
+      <c r="AD7">
+        <v>2647.3</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2647.3</v>
+      </c>
+      <c r="AG7">
+        <v>2391</v>
+      </c>
+      <c r="AH7">
+        <v>0.7267012544950452</v>
+      </c>
+      <c r="AI7">
+        <v>0.7322895632209344</v>
+      </c>
+      <c r="AJ7">
+        <v>0.706017834996752</v>
+      </c>
+      <c r="AK7">
+        <v>0.7118613790639514</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0148</v>
+        <v>0.01272</v>
       </c>
       <c r="E2">
-        <v>0.01885</v>
+        <v>0.01835</v>
       </c>
       <c r="F2">
-        <v>0.04735</v>
+        <v>0.0152</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20109.99</v>
+        <v>20771.6</v>
       </c>
       <c r="L2">
-        <v>0.3683971510117646</v>
+        <v>0.363278312363803</v>
       </c>
       <c r="M2">
-        <v>22601.7</v>
+        <v>16132.6</v>
       </c>
       <c r="N2">
-        <v>0.07893763522728663</v>
+        <v>0.0535811374309046</v>
       </c>
       <c r="O2">
-        <v>1.123904089460015</v>
+        <v>0.7766662173352078</v>
       </c>
       <c r="P2">
-        <v>12315.3</v>
+        <v>13269.5</v>
       </c>
       <c r="Q2">
-        <v>0.04301183800840657</v>
+        <v>0.04407193528255759</v>
       </c>
       <c r="R2">
-        <v>0.6123971220274101</v>
+        <v>0.6388289780276917</v>
       </c>
       <c r="S2">
-        <v>10286.4</v>
+        <v>2863.099999999999</v>
       </c>
       <c r="T2">
-        <v>0.455116208072844</v>
+        <v>0.1774729429850117</v>
       </c>
       <c r="U2">
-        <v>274848.6</v>
+        <v>227623.8</v>
       </c>
       <c r="V2">
-        <v>0.9599233035360352</v>
+        <v>0.7560059823180852</v>
       </c>
       <c r="W2">
-        <v>0.09763086538398101</v>
+        <v>0.1078699211500598</v>
       </c>
       <c r="X2">
-        <v>0.1192046037750007</v>
+        <v>0.09279250730645766</v>
       </c>
       <c r="Y2">
-        <v>-0.02157373839101968</v>
+        <v>0.01507741384360216</v>
       </c>
       <c r="Z2">
-        <v>0.08591355888322037</v>
+        <v>0.08760681534451492</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05588484603734435</v>
+        <v>0.04829254707326228</v>
       </c>
       <c r="AC2">
-        <v>-0.05588484603734435</v>
+        <v>-0.04829254707326228</v>
       </c>
       <c r="AD2">
-        <v>737153.1</v>
+        <v>692054.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>737153.1</v>
+        <v>692054.5</v>
       </c>
       <c r="AG2">
-        <v>462304.5</v>
+        <v>464430.7</v>
       </c>
       <c r="AH2">
-        <v>0.7202442146698811</v>
+        <v>0.6968335236720476</v>
       </c>
       <c r="AI2">
-        <v>0.8060365833989855</v>
+        <v>0.7930436980794957</v>
       </c>
       <c r="AJ2">
-        <v>0.6175356786013881</v>
+        <v>0.6066881510297601</v>
       </c>
       <c r="AK2">
-        <v>0.7226986929176373</v>
+        <v>0.7200114288832623</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Australia Bank Limited (ASX:NAB)</t>
+          <t>ANZ Group Holdings Limited (ASX:ANZ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0141</v>
+        <v>0.009340000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0545</v>
+        <v>0.0209</v>
       </c>
       <c r="F3">
-        <v>0.0707</v>
+        <v>0.0092</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4439.5</v>
+        <v>4580.2</v>
       </c>
       <c r="L3">
-        <v>0.3735757922550026</v>
+        <v>0.3511400052132048</v>
       </c>
       <c r="M3">
-        <v>5426.5</v>
+        <v>2840</v>
       </c>
       <c r="N3">
-        <v>0.08444915465252359</v>
+        <v>0.05351684838526101</v>
       </c>
       <c r="O3">
-        <v>1.222322333596126</v>
+        <v>0.6200602593773198</v>
       </c>
       <c r="P3">
-        <v>2580.9</v>
+        <v>2826.4</v>
       </c>
       <c r="Q3">
-        <v>0.04016489878240084</v>
+        <v>0.05326057051975412</v>
       </c>
       <c r="R3">
-        <v>0.581349251041784</v>
+        <v>0.6170909567267805</v>
       </c>
       <c r="S3">
-        <v>2845.6</v>
+        <v>13.59999999999991</v>
       </c>
       <c r="T3">
-        <v>0.5243895697042292</v>
+        <v>0.004788732394366165</v>
       </c>
       <c r="U3">
-        <v>26728.5</v>
+        <v>88044.8</v>
       </c>
       <c r="V3">
-        <v>0.415958579218645</v>
+        <v>1.659112750954447</v>
       </c>
       <c r="W3">
-        <v>0.09763086538398101</v>
+        <v>0.1078699211500598</v>
       </c>
       <c r="X3">
-        <v>0.1287475869805902</v>
+        <v>0.08889761623908535</v>
       </c>
       <c r="Y3">
-        <v>-0.03111672159660923</v>
+        <v>0.01897230491097447</v>
       </c>
       <c r="Z3">
-        <v>0.049383772893986</v>
+        <v>0.1557308742027684</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05552526584110484</v>
+        <v>0.04780987142061295</v>
       </c>
       <c r="AC3">
-        <v>-0.05552526584110484</v>
+        <v>-0.04780987142061295</v>
       </c>
       <c r="AD3">
-        <v>223145.9</v>
+        <v>133934.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>223145.9</v>
+        <v>133934.3</v>
       </c>
       <c r="AG3">
-        <v>196417.4</v>
+        <v>45889.49999999999</v>
       </c>
       <c r="AH3">
-        <v>0.7764202593218246</v>
+        <v>0.716219692120446</v>
       </c>
       <c r="AI3">
-        <v>0.8543853959631224</v>
+        <v>0.7476765996404925</v>
       </c>
       <c r="AJ3">
-        <v>0.7534953486141747</v>
+        <v>0.4637321904788851</v>
       </c>
       <c r="AK3">
-        <v>0.8377844866636014</v>
+        <v>0.5037863983875146</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Westpac Banking Corporation (ASX:WBC)</t>
+          <t>National Australia Bank Limited (ASX:NAB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0151</v>
+        <v>0.0161</v>
       </c>
       <c r="E4">
-        <v>-0.0655</v>
+        <v>0.0595</v>
       </c>
       <c r="F4">
-        <v>0.117</v>
+        <v>0.009860000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3668.3</v>
+        <v>4784.2</v>
       </c>
       <c r="L4">
-        <v>0.295466078145514</v>
+        <v>0.373844482820595</v>
       </c>
       <c r="M4">
-        <v>5103.7</v>
+        <v>3845.3</v>
       </c>
       <c r="N4">
-        <v>0.09177616376822278</v>
+        <v>0.05904953785248442</v>
       </c>
       <c r="O4">
-        <v>1.391298421612191</v>
+        <v>0.8037498432339786</v>
       </c>
       <c r="P4">
-        <v>2794.1</v>
+        <v>2799.9</v>
       </c>
       <c r="Q4">
-        <v>0.0502442892773461</v>
+        <v>0.0429960733969186</v>
       </c>
       <c r="R4">
-        <v>0.7616879753564321</v>
+        <v>0.5852389114167469</v>
       </c>
       <c r="S4">
-        <v>2309.6</v>
+        <v>1045.4</v>
       </c>
       <c r="T4">
-        <v>0.4525344358014773</v>
+        <v>0.2718643538865628</v>
       </c>
       <c r="U4">
-        <v>67616.3</v>
+        <v>1865.5</v>
       </c>
       <c r="V4">
-        <v>1.215895256813936</v>
+        <v>0.0286471570134475</v>
       </c>
       <c r="W4">
-        <v>0.07030546260200933</v>
+        <v>0.1257967142766991</v>
       </c>
       <c r="X4">
-        <v>0.1196461265906391</v>
+        <v>0.0968737867251957</v>
       </c>
       <c r="Y4">
-        <v>-0.04934066398862974</v>
+        <v>0.02892292755150344</v>
       </c>
       <c r="Z4">
-        <v>0.08347727744917356</v>
+        <v>0.04958008815494877</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0558661346790262</v>
+        <v>0.04805663346216517</v>
       </c>
       <c r="AC4">
-        <v>-0.0558661346790262</v>
+        <v>-0.04805663346216517</v>
       </c>
       <c r="AD4">
-        <v>165537.3</v>
+        <v>205331.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>165537.3</v>
+        <v>205331.4</v>
       </c>
       <c r="AG4">
-        <v>97920.99999999999</v>
+        <v>203465.9</v>
       </c>
       <c r="AH4">
-        <v>0.7485376282627531</v>
+        <v>0.7592176484269072</v>
       </c>
       <c r="AI4">
-        <v>0.7846764235349883</v>
+        <v>0.838024409595361</v>
       </c>
       <c r="AJ4">
-        <v>0.6377917727525266</v>
+        <v>0.7575452611418773</v>
       </c>
       <c r="AK4">
-        <v>0.6831084465441009</v>
+        <v>0.8367817122477256</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANZ Group Holdings Limited (ASX:ANZ)</t>
+          <t>Westpac Banking Corporation (ASX:WBC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0155</v>
+        <v>-0.00283</v>
       </c>
       <c r="E5">
-        <v>0.0213</v>
+        <v>-0.0233</v>
       </c>
       <c r="F5">
-        <v>0.013</v>
+        <v>0.0152</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4586.4</v>
+        <v>4642.8</v>
       </c>
       <c r="L5">
-        <v>0.3621432970642578</v>
+        <v>0.342664826446037</v>
       </c>
       <c r="M5">
-        <v>3058.2</v>
+        <v>2957.4</v>
       </c>
       <c r="N5">
-        <v>0.06393721266200166</v>
+        <v>0.05418696647165418</v>
       </c>
       <c r="O5">
-        <v>0.6667974882260598</v>
+        <v>0.636986301369863</v>
       </c>
       <c r="P5">
-        <v>2437.8</v>
+        <v>2906.4</v>
       </c>
       <c r="Q5">
-        <v>0.05096662645589813</v>
+        <v>0.05325251888591861</v>
       </c>
       <c r="R5">
-        <v>0.5315279958137101</v>
+        <v>0.6260015507883174</v>
       </c>
       <c r="S5">
-        <v>620.4000000000001</v>
+        <v>51</v>
       </c>
       <c r="T5">
-        <v>0.2028644300568962</v>
+        <v>0.01724487725705011</v>
       </c>
       <c r="U5">
-        <v>98013.10000000001</v>
+        <v>65963.10000000001</v>
       </c>
       <c r="V5">
-        <v>2.049141461762486</v>
+        <v>1.208609010639877</v>
       </c>
       <c r="W5">
-        <v>0.09945786529036735</v>
+        <v>0.1022902277008493</v>
       </c>
       <c r="X5">
-        <v>0.1192046037750007</v>
+        <v>0.09279250730645766</v>
       </c>
       <c r="Y5">
-        <v>-0.01974673848463335</v>
+        <v>0.009497720394391673</v>
       </c>
       <c r="Z5">
-        <v>0.1920852026779024</v>
+        <v>0.09779453266987426</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05588484603734435</v>
+        <v>0.04829254707326228</v>
       </c>
       <c r="AC5">
-        <v>-0.05588484603734435</v>
+        <v>-0.04829254707326228</v>
       </c>
       <c r="AD5">
-        <v>141230.5</v>
+        <v>154517</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>141230.5</v>
+        <v>154517</v>
       </c>
       <c r="AG5">
-        <v>43217.39999999999</v>
+        <v>88553.89999999999</v>
       </c>
       <c r="AH5">
-        <v>0.747007063298879</v>
+        <v>0.7389809497801714</v>
       </c>
       <c r="AI5">
-        <v>0.7675191063920208</v>
+        <v>0.7674987855481723</v>
       </c>
       <c r="AJ5">
-        <v>0.474662460858859</v>
+        <v>0.6186886753169811</v>
       </c>
       <c r="AK5">
-        <v>0.5025512814549513</v>
+        <v>0.6541991381647623</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0169</v>
+        <v>0.026</v>
       </c>
       <c r="E6">
-        <v>0.0164</v>
+        <v>0.0158</v>
       </c>
       <c r="F6">
-        <v>0.024</v>
+        <v>0.0231</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>7421.1</v>
+        <v>6715.5</v>
       </c>
       <c r="L6">
-        <v>0.423520750582112</v>
+        <v>0.3817924431760037</v>
       </c>
       <c r="M6">
-        <v>9013.299999999999</v>
+        <v>6489.9</v>
       </c>
       <c r="N6">
-        <v>0.07662500733239422</v>
+        <v>0.05087480137748195</v>
       </c>
       <c r="O6">
-        <v>1.214550403578984</v>
+        <v>0.9664060754969845</v>
       </c>
       <c r="P6">
-        <v>4502.5</v>
+        <v>4736.8</v>
       </c>
       <c r="Q6">
-        <v>0.03827722316067422</v>
+        <v>0.03713212209199779</v>
       </c>
       <c r="R6">
-        <v>0.6067159855008017</v>
+        <v>0.7053532871714691</v>
       </c>
       <c r="S6">
-        <v>4510.799999999999</v>
+        <v>1753.099999999999</v>
       </c>
       <c r="T6">
-        <v>0.5004604306968591</v>
+        <v>0.270127428773941</v>
       </c>
       <c r="U6">
-        <v>82234.39999999999</v>
+        <v>71329.10000000001</v>
       </c>
       <c r="V6">
-        <v>0.6991014947882617</v>
+        <v>0.5591540385729438</v>
       </c>
       <c r="W6">
-        <v>0.1257992663362242</v>
+        <v>0.1338250181342814</v>
       </c>
       <c r="X6">
-        <v>0.09693677260778816</v>
+        <v>0.07630856641789738</v>
       </c>
       <c r="Y6">
-        <v>0.028862493728436</v>
+        <v>0.057516451716384</v>
       </c>
       <c r="Z6">
-        <v>0.09907071730492188</v>
+        <v>0.104146646322148</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05725483416356029</v>
+        <v>0.04985627642563328</v>
       </c>
       <c r="AC6">
-        <v>-0.05725483416356029</v>
+        <v>-0.04985627642563328</v>
       </c>
       <c r="AD6">
-        <v>204592.1</v>
+        <v>195258.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>204592.1</v>
+        <v>195258.6</v>
       </c>
       <c r="AG6">
-        <v>122357.7</v>
+        <v>123929.5</v>
       </c>
       <c r="AH6">
-        <v>0.6349438025105767</v>
+        <v>0.6048440531347199</v>
       </c>
       <c r="AI6">
-        <v>0.8030251588940432</v>
+        <v>0.8029316302474565</v>
       </c>
       <c r="AJ6">
-        <v>0.5098526416496935</v>
+        <v>0.4927700524382931</v>
       </c>
       <c r="AK6">
-        <v>0.709146105042068</v>
+        <v>0.7211366691300123</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1212,6 +1212,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F7">
+        <v>0.316</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1225,10 +1228,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-5.31</v>
+        <v>48.9</v>
       </c>
       <c r="L7">
-        <v>-0.05221238938053097</v>
+        <v>0.2462235649546828</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1237,7 +1240,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1246,61 +1249,61 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>256.3</v>
+        <v>421.3</v>
       </c>
       <c r="V7">
-        <v>0.2574327038971475</v>
+        <v>0.5571277439830733</v>
       </c>
       <c r="W7">
-        <v>-0.006584004959702417</v>
+        <v>0.05052696838189709</v>
       </c>
       <c r="X7">
-        <v>0.113814997440816</v>
+        <v>0.1074135875233079</v>
       </c>
       <c r="Y7">
-        <v>-0.1203990024005184</v>
+        <v>-0.05688661914141079</v>
       </c>
       <c r="Z7">
-        <v>0.03166054417533155</v>
+        <v>0.05912826009289032</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05908349431828389</v>
+        <v>0.05000571843930742</v>
       </c>
       <c r="AC7">
-        <v>-0.05908349431828389</v>
+        <v>-0.05000571843930742</v>
       </c>
       <c r="AD7">
-        <v>2647.3</v>
+        <v>3013.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2647.3</v>
+        <v>3013.2</v>
       </c>
       <c r="AG7">
-        <v>2391</v>
+        <v>2591.9</v>
       </c>
       <c r="AH7">
-        <v>0.7267012544950452</v>
+        <v>0.7993845174298297</v>
       </c>
       <c r="AI7">
-        <v>0.7322895632209344</v>
+        <v>0.7539974476390662</v>
       </c>
       <c r="AJ7">
-        <v>0.706017834996752</v>
+        <v>0.7741405573310236</v>
       </c>
       <c r="AK7">
-        <v>0.7118613790639514</v>
+        <v>0.725006993006993</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01272</v>
+        <v>0.0321</v>
       </c>
       <c r="E2">
-        <v>0.01835</v>
+        <v>0.0186</v>
       </c>
       <c r="F2">
-        <v>0.0152</v>
+        <v>0.0452</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20771.6</v>
+        <v>15939.7</v>
       </c>
       <c r="L2">
-        <v>0.363278312363803</v>
+        <v>0.3478544570509506</v>
       </c>
       <c r="M2">
-        <v>16132.6</v>
+        <v>15288.2</v>
       </c>
       <c r="N2">
-        <v>0.0535811374309046</v>
+        <v>0.0513575578739163</v>
       </c>
       <c r="O2">
-        <v>0.7766662173352078</v>
+        <v>0.9591272106752323</v>
       </c>
       <c r="P2">
-        <v>13269.5</v>
+        <v>11902.4</v>
       </c>
       <c r="Q2">
-        <v>0.04407193528255759</v>
+        <v>0.03998366039419299</v>
       </c>
       <c r="R2">
-        <v>0.6388289780276917</v>
+        <v>0.7467141790623412</v>
       </c>
       <c r="S2">
-        <v>2863.099999999999</v>
+        <v>3385.800000000001</v>
       </c>
       <c r="T2">
-        <v>0.1774729429850117</v>
+        <v>0.2214649206577622</v>
       </c>
       <c r="U2">
-        <v>227623.8</v>
+        <v>78618.89999999999</v>
       </c>
       <c r="V2">
-        <v>0.7560059823180852</v>
+        <v>0.2641039956786043</v>
       </c>
       <c r="W2">
-        <v>0.1078699211500598</v>
+        <v>0.1222853493758521</v>
       </c>
       <c r="X2">
-        <v>0.09279250730645766</v>
+        <v>0.09382973762752808</v>
       </c>
       <c r="Y2">
-        <v>0.01507741384360216</v>
+        <v>0.02845561174832401</v>
       </c>
       <c r="Z2">
-        <v>0.08760681534451492</v>
+        <v>0.08482323009816065</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04829254707326228</v>
+        <v>0.05278174557672266</v>
       </c>
       <c r="AC2">
-        <v>-0.04829254707326228</v>
+        <v>-0.05278174557672266</v>
       </c>
       <c r="AD2">
-        <v>692054.5</v>
+        <v>576146.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>692054.5</v>
+        <v>576146.1</v>
       </c>
       <c r="AG2">
-        <v>464430.7</v>
+        <v>497527.2</v>
       </c>
       <c r="AH2">
-        <v>0.6968335236720476</v>
+        <v>0.6593360453096189</v>
       </c>
       <c r="AI2">
-        <v>0.7930436980794957</v>
+        <v>0.8024304412819308</v>
       </c>
       <c r="AJ2">
-        <v>0.6066881510297601</v>
+        <v>0.6256560541080531</v>
       </c>
       <c r="AK2">
-        <v>0.7200114288832623</v>
+        <v>0.7781371523520197</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANZ Group Holdings Limited (ASX:ANZ)</t>
+          <t>National Australia Bank Limited (ASX:NAB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.009340000000000001</v>
+        <v>0.0369</v>
       </c>
       <c r="E3">
-        <v>0.0209</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="F3">
-        <v>0.0092</v>
+        <v>0.0341</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4580.2</v>
+        <v>4825.6</v>
       </c>
       <c r="L3">
-        <v>0.3511400052132048</v>
+        <v>0.3496583556144889</v>
       </c>
       <c r="M3">
-        <v>2840</v>
+        <v>5069</v>
       </c>
       <c r="N3">
-        <v>0.05351684838526101</v>
+        <v>0.0719649162160282</v>
       </c>
       <c r="O3">
-        <v>0.6200602593773198</v>
+        <v>1.050439323607427</v>
       </c>
       <c r="P3">
-        <v>2826.4</v>
+        <v>3258.7</v>
       </c>
       <c r="Q3">
-        <v>0.05326057051975412</v>
+        <v>0.04626397168537602</v>
       </c>
       <c r="R3">
-        <v>0.6170909567267805</v>
+        <v>0.6752942639257293</v>
       </c>
       <c r="S3">
-        <v>13.59999999999991</v>
+        <v>1810.3</v>
       </c>
       <c r="T3">
-        <v>0.004788732394366165</v>
+        <v>0.3571315841388835</v>
       </c>
       <c r="U3">
-        <v>88044.8</v>
+        <v>1732.6</v>
       </c>
       <c r="V3">
-        <v>1.659112750954447</v>
+        <v>0.0245978326762459</v>
       </c>
       <c r="W3">
-        <v>0.1078699211500598</v>
+        <v>0.1222853493758521</v>
       </c>
       <c r="X3">
-        <v>0.08889761623908535</v>
+        <v>0.09957931231953709</v>
       </c>
       <c r="Y3">
-        <v>0.01897230491097447</v>
+        <v>0.02270603705631499</v>
       </c>
       <c r="Z3">
-        <v>0.1557308742027684</v>
+        <v>0.05712482201397397</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04780987142061295</v>
+        <v>0.05232297622222741</v>
       </c>
       <c r="AC3">
-        <v>-0.04780987142061295</v>
+        <v>-0.05232297622222741</v>
       </c>
       <c r="AD3">
-        <v>133934.3</v>
+        <v>216663.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>133934.3</v>
+        <v>216663.7</v>
       </c>
       <c r="AG3">
-        <v>45889.49999999999</v>
+        <v>214931.1</v>
       </c>
       <c r="AH3">
-        <v>0.716219692120446</v>
+        <v>0.7546607323978198</v>
       </c>
       <c r="AI3">
-        <v>0.7476765996404925</v>
+        <v>0.8339688904815774</v>
       </c>
       <c r="AJ3">
-        <v>0.4637321904788851</v>
+        <v>0.7531711662336589</v>
       </c>
       <c r="AK3">
-        <v>0.5037863983875146</v>
+        <v>0.8328541917813952</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Australia Bank Limited (ASX:NAB)</t>
+          <t>Westpac Banking Corporation (ASX:WBC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0161</v>
+        <v>0.0118</v>
       </c>
       <c r="E4">
-        <v>0.0595</v>
+        <v>0.006</v>
       </c>
       <c r="F4">
-        <v>0.009860000000000001</v>
+        <v>0.0489</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>4784.2</v>
+        <v>4846.4</v>
       </c>
       <c r="L4">
-        <v>0.373844482820595</v>
+        <v>0.3320498239171246</v>
       </c>
       <c r="M4">
-        <v>3845.3</v>
+        <v>4891.6</v>
       </c>
       <c r="N4">
-        <v>0.05904953785248442</v>
+        <v>0.07122451535121566</v>
       </c>
       <c r="O4">
-        <v>0.8037498432339786</v>
+        <v>1.009326510399472</v>
       </c>
       <c r="P4">
-        <v>2799.9</v>
+        <v>3557.6</v>
       </c>
       <c r="Q4">
-        <v>0.0429960733969186</v>
+        <v>0.05180070647916526</v>
       </c>
       <c r="R4">
-        <v>0.5852389114167469</v>
+        <v>0.7340706503796632</v>
       </c>
       <c r="S4">
-        <v>1045.4</v>
+        <v>1334</v>
       </c>
       <c r="T4">
-        <v>0.2718643538865628</v>
+        <v>0.2727124049390793</v>
       </c>
       <c r="U4">
-        <v>1865.5</v>
+        <v>45313.7</v>
       </c>
       <c r="V4">
-        <v>0.0286471570134475</v>
+        <v>0.6597935892694375</v>
       </c>
       <c r="W4">
-        <v>0.1257967142766991</v>
+        <v>0.1035998289867465</v>
       </c>
       <c r="X4">
-        <v>0.0968737867251957</v>
+        <v>0.09382973762752808</v>
       </c>
       <c r="Y4">
-        <v>0.02892292755150344</v>
+        <v>0.009770091359218386</v>
       </c>
       <c r="Z4">
-        <v>0.04958008815494877</v>
+        <v>0.1118023079898733</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04805663346216517</v>
+        <v>0.05278174557672266</v>
       </c>
       <c r="AC4">
-        <v>-0.04805663346216517</v>
+        <v>-0.05278174557672266</v>
       </c>
       <c r="AD4">
-        <v>205331.4</v>
+        <v>178180</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>205331.4</v>
+        <v>178180</v>
       </c>
       <c r="AG4">
-        <v>203465.9</v>
+        <v>132866.3</v>
       </c>
       <c r="AH4">
-        <v>0.7592176484269072</v>
+        <v>0.7217897209171567</v>
       </c>
       <c r="AI4">
-        <v>0.838024409595361</v>
+        <v>0.7810243262470725</v>
       </c>
       <c r="AJ4">
-        <v>0.7575452611418773</v>
+        <v>0.659239206747479</v>
       </c>
       <c r="AK4">
-        <v>0.8367817122477256</v>
+        <v>0.7267498657168205</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Westpac Banking Corporation (ASX:WBC)</t>
+          <t>Commonwealth Bank of Australia (ASX:CBA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00283</v>
+        <v>0.0321</v>
       </c>
       <c r="E5">
-        <v>-0.0233</v>
+        <v>0.0186</v>
       </c>
       <c r="F5">
-        <v>0.0152</v>
+        <v>0.0452</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,331 +984,90 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4642.8</v>
+        <v>6267.7</v>
       </c>
       <c r="L5">
-        <v>0.342664826446037</v>
+        <v>0.359662814318341</v>
       </c>
       <c r="M5">
-        <v>2957.4</v>
+        <v>5327.6</v>
       </c>
       <c r="N5">
-        <v>0.05418696647165418</v>
+        <v>0.03359864888983067</v>
       </c>
       <c r="O5">
-        <v>0.636986301369863</v>
+        <v>0.8500087751487787</v>
       </c>
       <c r="P5">
-        <v>2906.4</v>
+        <v>5086.1</v>
       </c>
       <c r="Q5">
-        <v>0.05325251888591861</v>
+        <v>0.03207562281675947</v>
       </c>
       <c r="R5">
-        <v>0.6260015507883174</v>
+        <v>0.8114778946024859</v>
       </c>
       <c r="S5">
-        <v>51</v>
+        <v>241.5</v>
       </c>
       <c r="T5">
-        <v>0.01724487725705011</v>
+        <v>0.04532997972820782</v>
       </c>
       <c r="U5">
-        <v>65963.10000000001</v>
+        <v>31572.6</v>
       </c>
       <c r="V5">
-        <v>1.208609010639877</v>
+        <v>0.1991134285492656</v>
       </c>
       <c r="W5">
-        <v>0.1022902277008493</v>
+        <v>0.1314741202999633</v>
       </c>
       <c r="X5">
-        <v>0.09279250730645766</v>
+        <v>0.07650626956533674</v>
       </c>
       <c r="Y5">
-        <v>0.009497720394391673</v>
+        <v>0.05496785073462654</v>
       </c>
       <c r="Z5">
-        <v>0.09779453266987426</v>
+        <v>0.10368168569455</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04829254707326228</v>
+        <v>0.05541035216661933</v>
       </c>
       <c r="AC5">
-        <v>-0.04829254707326228</v>
+        <v>-0.05541035216661933</v>
       </c>
       <c r="AD5">
-        <v>154517</v>
+        <v>181302.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>154517</v>
+        <v>181302.4</v>
       </c>
       <c r="AG5">
-        <v>88553.89999999999</v>
+        <v>149729.8</v>
       </c>
       <c r="AH5">
-        <v>0.7389809497801714</v>
+        <v>0.5334489859748615</v>
       </c>
       <c r="AI5">
-        <v>0.7674987855481723</v>
+        <v>0.7880427719439623</v>
       </c>
       <c r="AJ5">
-        <v>0.6186886753169811</v>
+        <v>0.4856694400862549</v>
       </c>
       <c r="AK5">
-        <v>0.6541991381647623</v>
+        <v>0.7543287180828046</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Commonwealth Bank of Australia (ASX:CBA)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.026</v>
-      </c>
-      <c r="E6">
-        <v>0.0158</v>
-      </c>
-      <c r="F6">
-        <v>0.0231</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>6715.5</v>
-      </c>
-      <c r="L6">
-        <v>0.3817924431760037</v>
-      </c>
-      <c r="M6">
-        <v>6489.9</v>
-      </c>
-      <c r="N6">
-        <v>0.05087480137748195</v>
-      </c>
-      <c r="O6">
-        <v>0.9664060754969845</v>
-      </c>
-      <c r="P6">
-        <v>4736.8</v>
-      </c>
-      <c r="Q6">
-        <v>0.03713212209199779</v>
-      </c>
-      <c r="R6">
-        <v>0.7053532871714691</v>
-      </c>
-      <c r="S6">
-        <v>1753.099999999999</v>
-      </c>
-      <c r="T6">
-        <v>0.270127428773941</v>
-      </c>
-      <c r="U6">
-        <v>71329.10000000001</v>
-      </c>
-      <c r="V6">
-        <v>0.5591540385729438</v>
-      </c>
-      <c r="W6">
-        <v>0.1338250181342814</v>
-      </c>
-      <c r="X6">
-        <v>0.07630856641789738</v>
-      </c>
-      <c r="Y6">
-        <v>0.057516451716384</v>
-      </c>
-      <c r="Z6">
-        <v>0.104146646322148</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.04985627642563328</v>
-      </c>
-      <c r="AC6">
-        <v>-0.04985627642563328</v>
-      </c>
-      <c r="AD6">
-        <v>195258.6</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>195258.6</v>
-      </c>
-      <c r="AG6">
-        <v>123929.5</v>
-      </c>
-      <c r="AH6">
-        <v>0.6048440531347199</v>
-      </c>
-      <c r="AI6">
-        <v>0.8029316302474565</v>
-      </c>
-      <c r="AJ6">
-        <v>0.4927700524382931</v>
-      </c>
-      <c r="AK6">
-        <v>0.7211366691300123</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Judo Capital Holdings Limited (ASX:JDO)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>0.316</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>48.9</v>
-      </c>
-      <c r="L7">
-        <v>0.2462235649546828</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>421.3</v>
-      </c>
-      <c r="V7">
-        <v>0.5571277439830733</v>
-      </c>
-      <c r="W7">
-        <v>0.05052696838189709</v>
-      </c>
-      <c r="X7">
-        <v>0.1074135875233079</v>
-      </c>
-      <c r="Y7">
-        <v>-0.05688661914141079</v>
-      </c>
-      <c r="Z7">
-        <v>0.05912826009289032</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05000571843930742</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05000571843930742</v>
-      </c>
-      <c r="AD7">
-        <v>3013.2</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>3013.2</v>
-      </c>
-      <c r="AG7">
-        <v>2591.9</v>
-      </c>
-      <c r="AH7">
-        <v>0.7993845174298297</v>
-      </c>
-      <c r="AI7">
-        <v>0.7539974476390662</v>
-      </c>
-      <c r="AJ7">
-        <v>0.7741405573310236</v>
-      </c>
-      <c r="AK7">
-        <v>0.725006993006993</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0321</v>
+        <v>0.02745</v>
       </c>
       <c r="E2">
-        <v>0.0186</v>
+        <v>0.0187</v>
       </c>
       <c r="F2">
         <v>0.0452</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>15939.7</v>
+        <v>20517.3</v>
       </c>
       <c r="L2">
-        <v>0.3478544570509506</v>
+        <v>0.3419247966429632</v>
       </c>
       <c r="M2">
-        <v>15288.2</v>
+        <v>19607</v>
       </c>
       <c r="N2">
-        <v>0.0513575578739163</v>
+        <v>0.05578930326111483</v>
       </c>
       <c r="O2">
-        <v>0.9591272106752323</v>
+        <v>0.9556325637388936</v>
       </c>
       <c r="P2">
-        <v>11902.4</v>
+        <v>15521.6</v>
       </c>
       <c r="Q2">
-        <v>0.03998366039419299</v>
+        <v>0.04416480081081858</v>
       </c>
       <c r="R2">
-        <v>0.7467141790623412</v>
+        <v>0.7565127965180604</v>
       </c>
       <c r="S2">
-        <v>3385.800000000001</v>
+        <v>4085.400000000001</v>
       </c>
       <c r="T2">
-        <v>0.2214649206577622</v>
+        <v>0.2083643596674657</v>
       </c>
       <c r="U2">
-        <v>78618.89999999999</v>
+        <v>153133.1</v>
       </c>
       <c r="V2">
-        <v>0.2641039956786043</v>
+        <v>0.4357213727349734</v>
       </c>
       <c r="W2">
-        <v>0.1222853493758521</v>
+        <v>0.1035998289867465</v>
       </c>
       <c r="X2">
-        <v>0.09382973762752808</v>
+        <v>0.09379885877658306</v>
       </c>
       <c r="Y2">
-        <v>0.02845561174832401</v>
+        <v>0.009800970210163407</v>
       </c>
       <c r="Z2">
-        <v>0.08482323009816065</v>
+        <v>0.09486207561072738</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05278174557672266</v>
+        <v>0.05277315476298349</v>
       </c>
       <c r="AC2">
-        <v>-0.05278174557672266</v>
+        <v>-0.05277315476298349</v>
       </c>
       <c r="AD2">
-        <v>576146.1</v>
+        <v>758752.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>576146.1</v>
+        <v>758752.6</v>
       </c>
       <c r="AG2">
-        <v>497527.2</v>
+        <v>605619.5</v>
       </c>
       <c r="AH2">
-        <v>0.6593360453096189</v>
+        <v>0.6834378205222321</v>
       </c>
       <c r="AI2">
-        <v>0.8024304412819308</v>
+        <v>0.7981650314552211</v>
       </c>
       <c r="AJ2">
-        <v>0.6256560541080531</v>
+        <v>0.6327870740057016</v>
       </c>
       <c r="AK2">
-        <v>0.7781371523520197</v>
+        <v>0.7594088237805681</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Australia Bank Limited (ASX:NAB)</t>
+          <t>ANZ Group Holdings Limited (ASX:ANZ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0369</v>
+        <v>0.0228</v>
       </c>
       <c r="E3">
-        <v>0.07719999999999999</v>
+        <v>0.0188</v>
       </c>
       <c r="F3">
-        <v>0.0341</v>
+        <v>0.0223</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4825.6</v>
+        <v>4531</v>
       </c>
       <c r="L3">
-        <v>0.3496583556144889</v>
+        <v>0.3244656092233879</v>
       </c>
       <c r="M3">
-        <v>5069</v>
+        <v>4318.8</v>
       </c>
       <c r="N3">
-        <v>0.0719649162160282</v>
+        <v>0.08225142027870411</v>
       </c>
       <c r="O3">
-        <v>1.050439323607427</v>
+        <v>0.9531670712866918</v>
       </c>
       <c r="P3">
-        <v>3258.7</v>
+        <v>3619.2</v>
       </c>
       <c r="Q3">
-        <v>0.04626397168537602</v>
+        <v>0.0689275586442266</v>
       </c>
       <c r="R3">
-        <v>0.6752942639257293</v>
+        <v>0.7987640697417788</v>
       </c>
       <c r="S3">
-        <v>1810.3</v>
+        <v>699.6000000000004</v>
       </c>
       <c r="T3">
-        <v>0.3571315841388835</v>
+        <v>0.1619894415115311</v>
       </c>
       <c r="U3">
-        <v>1732.6</v>
+        <v>74077.5</v>
       </c>
       <c r="V3">
-        <v>0.0245978326762459</v>
+        <v>1.410803831086344</v>
       </c>
       <c r="W3">
-        <v>0.1222853493758521</v>
+        <v>0.1010387073467695</v>
       </c>
       <c r="X3">
-        <v>0.09957931231953709</v>
+        <v>0.1038603297912689</v>
       </c>
       <c r="Y3">
-        <v>0.02270603705631499</v>
+        <v>-0.002821622444499364</v>
       </c>
       <c r="Z3">
-        <v>0.05712482201397397</v>
+        <v>0.1573257384660276</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05232297622222741</v>
+        <v>0.05149320660040278</v>
       </c>
       <c r="AC3">
-        <v>-0.05232297622222741</v>
+        <v>-0.05149320660040278</v>
       </c>
       <c r="AD3">
-        <v>216663.7</v>
+        <v>180504.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>216663.7</v>
+        <v>180504.1</v>
       </c>
       <c r="AG3">
-        <v>214931.1</v>
+        <v>106426.6</v>
       </c>
       <c r="AH3">
-        <v>0.7546607323978198</v>
+        <v>0.7746578064420881</v>
       </c>
       <c r="AI3">
-        <v>0.8339688904815774</v>
+        <v>0.7866024383685931</v>
       </c>
       <c r="AJ3">
-        <v>0.7531711662336589</v>
+        <v>0.669628065503961</v>
       </c>
       <c r="AK3">
-        <v>0.8328541917813952</v>
+        <v>0.6848752474330032</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Westpac Banking Corporation (ASX:WBC)</t>
+          <t>National Australia Bank Limited (ASX:NAB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0118</v>
+        <v>0.0369</v>
       </c>
       <c r="E4">
-        <v>0.006</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="F4">
-        <v>0.0489</v>
+        <v>0.0341</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>4846.4</v>
+        <v>4825.6</v>
       </c>
       <c r="L4">
-        <v>0.3320498239171246</v>
+        <v>0.3496583556144889</v>
       </c>
       <c r="M4">
-        <v>4891.6</v>
+        <v>5069</v>
       </c>
       <c r="N4">
-        <v>0.07122451535121566</v>
+        <v>0.0719649162160282</v>
       </c>
       <c r="O4">
-        <v>1.009326510399472</v>
+        <v>1.050439323607427</v>
       </c>
       <c r="P4">
-        <v>3557.6</v>
+        <v>3258.7</v>
       </c>
       <c r="Q4">
-        <v>0.05180070647916526</v>
+        <v>0.04626397168537602</v>
       </c>
       <c r="R4">
-        <v>0.7340706503796632</v>
+        <v>0.6752942639257293</v>
       </c>
       <c r="S4">
-        <v>1334</v>
+        <v>1810.3</v>
       </c>
       <c r="T4">
-        <v>0.2727124049390793</v>
+        <v>0.3571315841388835</v>
       </c>
       <c r="U4">
-        <v>45313.7</v>
+        <v>1732.6</v>
       </c>
       <c r="V4">
-        <v>0.6597935892694375</v>
+        <v>0.0245978326762459</v>
       </c>
       <c r="W4">
-        <v>0.1035998289867465</v>
+        <v>0.1222853493758521</v>
       </c>
       <c r="X4">
-        <v>0.09382973762752808</v>
+        <v>0.09954473700326284</v>
       </c>
       <c r="Y4">
-        <v>0.009770091359218386</v>
+        <v>0.02274061237258924</v>
       </c>
       <c r="Z4">
-        <v>0.1118023079898733</v>
+        <v>0.05712482201397397</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05278174557672266</v>
+        <v>0.05231449353945557</v>
       </c>
       <c r="AC4">
-        <v>-0.05278174557672266</v>
+        <v>-0.05231449353945557</v>
       </c>
       <c r="AD4">
-        <v>178180</v>
+        <v>216663.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>178180</v>
+        <v>216663.7</v>
       </c>
       <c r="AG4">
-        <v>132866.3</v>
+        <v>214931.1</v>
       </c>
       <c r="AH4">
-        <v>0.7217897209171567</v>
+        <v>0.7546607323978198</v>
       </c>
       <c r="AI4">
-        <v>0.7810243262470725</v>
+        <v>0.8339688904815774</v>
       </c>
       <c r="AJ4">
-        <v>0.659239206747479</v>
+        <v>0.7531711662336589</v>
       </c>
       <c r="AK4">
-        <v>0.7267498657168205</v>
+        <v>0.8328541917813952</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,120 +954,361 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Westpac Banking Corporation (ASX:WBC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0118</v>
+      </c>
+      <c r="E5">
+        <v>0.006</v>
+      </c>
+      <c r="F5">
+        <v>0.0489</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>4846.4</v>
+      </c>
+      <c r="L5">
+        <v>0.3320498239171246</v>
+      </c>
+      <c r="M5">
+        <v>4891.6</v>
+      </c>
+      <c r="N5">
+        <v>0.07122451535121566</v>
+      </c>
+      <c r="O5">
+        <v>1.009326510399472</v>
+      </c>
+      <c r="P5">
+        <v>3557.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.05180070647916526</v>
+      </c>
+      <c r="R5">
+        <v>0.7340706503796632</v>
+      </c>
+      <c r="S5">
+        <v>1334</v>
+      </c>
+      <c r="T5">
+        <v>0.2727124049390793</v>
+      </c>
+      <c r="U5">
+        <v>45313.7</v>
+      </c>
+      <c r="V5">
+        <v>0.6597935892694375</v>
+      </c>
+      <c r="W5">
+        <v>0.1035998289867465</v>
+      </c>
+      <c r="X5">
+        <v>0.09379885877658306</v>
+      </c>
+      <c r="Y5">
+        <v>0.009800970210163407</v>
+      </c>
+      <c r="Z5">
+        <v>0.1118023079898733</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05277315476298349</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05277315476298349</v>
+      </c>
+      <c r="AD5">
+        <v>178180</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>178180</v>
+      </c>
+      <c r="AG5">
+        <v>132866.3</v>
+      </c>
+      <c r="AH5">
+        <v>0.7217897209171567</v>
+      </c>
+      <c r="AI5">
+        <v>0.7810243262470725</v>
+      </c>
+      <c r="AJ5">
+        <v>0.659239206747479</v>
+      </c>
+      <c r="AK5">
+        <v>0.7267498657168205</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Judo Capital Holdings Limited (ASX:JDO)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>0.412</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>46.6</v>
+      </c>
+      <c r="L6">
+        <v>0.2138595686094539</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>436.7</v>
+      </c>
+      <c r="V6">
+        <v>0.347027972027972</v>
+      </c>
+      <c r="W6">
+        <v>0.04740107822195097</v>
+      </c>
+      <c r="X6">
+        <v>0.08277789711833028</v>
+      </c>
+      <c r="Y6">
+        <v>-0.03537681889637931</v>
+      </c>
+      <c r="Z6">
+        <v>0.06095104895104896</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05521054800455452</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05521054800455452</v>
+      </c>
+      <c r="AD6">
+        <v>2102.4</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2102.4</v>
+      </c>
+      <c r="AG6">
+        <v>1665.7</v>
+      </c>
+      <c r="AH6">
+        <v>0.6255653415853368</v>
+      </c>
+      <c r="AI6">
+        <v>0.6681072835896784</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5696453609657672</v>
+      </c>
+      <c r="AK6">
+        <v>0.6146267665399801</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Commonwealth Bank of Australia (ASX:CBA)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D7">
         <v>0.0321</v>
       </c>
-      <c r="E5">
+      <c r="E7">
         <v>0.0186</v>
       </c>
-      <c r="F5">
+      <c r="F7">
         <v>0.0452</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>6267.7</v>
       </c>
-      <c r="L5">
+      <c r="L7">
         <v>0.359662814318341</v>
       </c>
-      <c r="M5">
+      <c r="M7">
         <v>5327.6</v>
       </c>
-      <c r="N5">
+      <c r="N7">
         <v>0.03359864888983067</v>
       </c>
-      <c r="O5">
+      <c r="O7">
         <v>0.8500087751487787</v>
       </c>
-      <c r="P5">
+      <c r="P7">
         <v>5086.1</v>
       </c>
-      <c r="Q5">
+      <c r="Q7">
         <v>0.03207562281675947</v>
       </c>
-      <c r="R5">
+      <c r="R7">
         <v>0.8114778946024859</v>
       </c>
-      <c r="S5">
+      <c r="S7">
         <v>241.5</v>
       </c>
-      <c r="T5">
+      <c r="T7">
         <v>0.04532997972820782</v>
       </c>
-      <c r="U5">
+      <c r="U7">
         <v>31572.6</v>
       </c>
-      <c r="V5">
+      <c r="V7">
         <v>0.1991134285492656</v>
       </c>
-      <c r="W5">
+      <c r="W7">
         <v>0.1314741202999633</v>
       </c>
-      <c r="X5">
-        <v>0.07650626956533674</v>
-      </c>
-      <c r="Y5">
-        <v>0.05496785073462654</v>
-      </c>
-      <c r="Z5">
+      <c r="X7">
+        <v>0.07648652816411695</v>
+      </c>
+      <c r="Y7">
+        <v>0.05498759213584632</v>
+      </c>
+      <c r="Z7">
         <v>0.10368168569455</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05541035216661933</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05541035216661933</v>
-      </c>
-      <c r="AD5">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05540114179586196</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05540114179586196</v>
+      </c>
+      <c r="AD7">
         <v>181302.4</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>181302.4</v>
       </c>
-      <c r="AG5">
+      <c r="AG7">
         <v>149729.8</v>
       </c>
-      <c r="AH5">
+      <c r="AH7">
         <v>0.5334489859748615</v>
       </c>
-      <c r="AI5">
+      <c r="AI7">
         <v>0.7880427719439623</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ7">
         <v>0.4856694400862549</v>
       </c>
-      <c r="AK5">
+      <c r="AK7">
         <v>0.7543287180828046</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>
